--- a/danhmuc.xlsx
+++ b/danhmuc.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SCM Inovation2\SCM_Inovation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3054E850-9686-478B-9F6F-0180D8CD0CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2E27C8-CD06-423C-8C25-8EA2FE649235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-810" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{24CD28A1-8F3D-4897-836A-81EDAD3DB0FF}"/>
+    <workbookView xWindow="-28920" yWindow="-810" windowWidth="29040" windowHeight="15720" xr2:uid="{24CD28A1-8F3D-4897-836A-81EDAD3DB0FF}"/>
   </bookViews>
   <sheets>
     <sheet name="ScrapDetails" sheetId="1" r:id="rId1"/>
     <sheet name="Scraps" sheetId="2" r:id="rId2"/>
+    <sheet name="MaterNametemplate" sheetId="3" r:id="rId3"/>
+    <sheet name="tbl_MV_Master_ACC" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="201">
   <si>
     <t>Id</t>
   </si>
@@ -443,6 +445,204 @@
   </si>
   <si>
     <t>IAF18951</t>
+  </si>
+  <si>
+    <t>NameTemplate</t>
+  </si>
+  <si>
+    <t>TypeID</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>MVTypeCode</t>
+  </si>
+  <si>
+    <t>MVTypeName</t>
+  </si>
+  <si>
+    <t>ContentMV</t>
+  </si>
+  <si>
+    <t>DateInsert</t>
+  </si>
+  <si>
+    <t>UserInsert</t>
+  </si>
+  <si>
+    <t>DateUpdate</t>
+  </si>
+  <si>
+    <t>UserUpdate</t>
+  </si>
+  <si>
+    <t>Flag_Delete</t>
+  </si>
+  <si>
+    <t>Other issue materials201</t>
+  </si>
+  <si>
+    <t>Out</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Other issue materials202</t>
+  </si>
+  <si>
+    <t>In</t>
+  </si>
+  <si>
+    <t>Other issue201</t>
+  </si>
+  <si>
+    <t>Other issue202</t>
+  </si>
+  <si>
+    <t>Issue sub-materials201</t>
+  </si>
+  <si>
+    <t>Issue sub-materials202</t>
+  </si>
+  <si>
+    <t>Issue Sub-Materials201</t>
+  </si>
+  <si>
+    <t>Return materials291</t>
+  </si>
+  <si>
+    <t>Return materials292</t>
+  </si>
+  <si>
+    <t>Claim scrap material201</t>
+  </si>
+  <si>
+    <t>Claim scrap material202</t>
+  </si>
+  <si>
+    <t>Claim Scrap Material (Claim transportation compa</t>
+  </si>
+  <si>
+    <t>Material shortage201</t>
+  </si>
+  <si>
+    <t>Material shortage202</t>
+  </si>
+  <si>
+    <t>Production rejects for outsourcing555</t>
+  </si>
+  <si>
+    <t>Production rejects for outsourcing556</t>
+  </si>
+  <si>
+    <t>Production rejects555</t>
+  </si>
+  <si>
+    <t>Production rejects556</t>
+  </si>
+  <si>
+    <t>Disposition551</t>
+  </si>
+  <si>
+    <t>Disposition552</t>
+  </si>
+  <si>
+    <t>Outsourcing201</t>
+  </si>
+  <si>
+    <t>Outsourcing202</t>
+  </si>
+  <si>
+    <t>Post difference outsourcing701</t>
+  </si>
+  <si>
+    <t>Post difference outsourcing702</t>
+  </si>
+  <si>
+    <t>Post difference end of month701</t>
+  </si>
+  <si>
+    <t>Post difference end of month702</t>
+  </si>
+  <si>
+    <t>Scrap mixing part559</t>
+  </si>
+  <si>
+    <t>Scrap mixing part560</t>
+  </si>
+  <si>
+    <t>Claim scrap halb201</t>
+  </si>
+  <si>
+    <t>Claim scrap halb202</t>
+  </si>
+  <si>
+    <t>Issue for lending201</t>
+  </si>
+  <si>
+    <t>Issue for lending202</t>
+  </si>
+  <si>
+    <t>Sale deadstock201</t>
+  </si>
+  <si>
+    <t>Sale deadstock202</t>
+  </si>
+  <si>
+    <t>Claim scrap deadstock201</t>
+  </si>
+  <si>
+    <t>Claim scrap deadstock202</t>
+  </si>
+  <si>
+    <t>Claim insurance201</t>
+  </si>
+  <si>
+    <t>Claim insurance202</t>
+  </si>
+  <si>
+    <t>Compensation201</t>
+  </si>
+  <si>
+    <t>Compensation202</t>
+  </si>
+  <si>
+    <t>Issue out for rework201</t>
+  </si>
+  <si>
+    <t>Issue out for rework202</t>
+  </si>
+  <si>
+    <t>Issue Out For Rework (Not issue Debit Note)201</t>
+  </si>
+  <si>
+    <t>Issue Out For Rework (Not issue Debit Note)202</t>
+  </si>
+  <si>
+    <t>Issue for investigation201</t>
+  </si>
+  <si>
+    <t>Issue for investigation202</t>
+  </si>
+  <si>
+    <t>Claim investigation halb201</t>
+  </si>
+  <si>
+    <t>Claim investigation halb202</t>
+  </si>
+  <si>
+    <t>TF trfr within plant</t>
+  </si>
+  <si>
+    <t>TR blocked to unre</t>
   </si>
 </sst>
 </file>
@@ -7352,4 +7552,1749 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E11ED9-094A-4E34-902C-E4D83A2AC484}">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617C8F75-5E10-424B-9C5C-5796BD725456}">
+  <dimension ref="A1:J52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>201</v>
+      </c>
+      <c r="C2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G2">
+        <v>2013168</v>
+      </c>
+      <c r="H2" s="1">
+        <v>44396.628140277775</v>
+      </c>
+      <c r="J2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>202</v>
+      </c>
+      <c r="C3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G3">
+        <v>2013168</v>
+      </c>
+      <c r="H3" s="1">
+        <v>44396.628141400462</v>
+      </c>
+      <c r="J3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>201</v>
+      </c>
+      <c r="C4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G4">
+        <v>2013168</v>
+      </c>
+      <c r="H4" s="1">
+        <v>44396.628142048612</v>
+      </c>
+      <c r="J4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>202</v>
+      </c>
+      <c r="C5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G5">
+        <v>2013168</v>
+      </c>
+      <c r="H5" s="1">
+        <v>44396.62814267361</v>
+      </c>
+      <c r="J5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>201</v>
+      </c>
+      <c r="C6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G6">
+        <v>2013168</v>
+      </c>
+      <c r="H6" s="1">
+        <v>44396.628143402777</v>
+      </c>
+      <c r="J6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>202</v>
+      </c>
+      <c r="C7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G7">
+        <v>2013168</v>
+      </c>
+      <c r="H7" s="1">
+        <v>44396.628144062503</v>
+      </c>
+      <c r="J7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>201</v>
+      </c>
+      <c r="C8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8">
+        <v>16</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G8">
+        <v>2013168</v>
+      </c>
+      <c r="H8" s="1">
+        <v>44396.62814479167</v>
+      </c>
+      <c r="J8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>291</v>
+      </c>
+      <c r="C9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G9">
+        <v>2013168</v>
+      </c>
+      <c r="H9" s="1">
+        <v>44396.628145289353</v>
+      </c>
+      <c r="J9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>292</v>
+      </c>
+      <c r="C10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G10">
+        <v>2013168</v>
+      </c>
+      <c r="H10" s="1">
+        <v>44396.628145833332</v>
+      </c>
+      <c r="J10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>201</v>
+      </c>
+      <c r="C11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G11">
+        <v>2013168</v>
+      </c>
+      <c r="H11" s="1">
+        <v>44396.628146331015</v>
+      </c>
+      <c r="J11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>202</v>
+      </c>
+      <c r="C12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G12">
+        <v>2013168</v>
+      </c>
+      <c r="H12" s="1">
+        <v>44396.628146840281</v>
+      </c>
+      <c r="J12" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>201</v>
+      </c>
+      <c r="C13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D13" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G13">
+        <v>2013168</v>
+      </c>
+      <c r="H13" s="1">
+        <v>44396.628147372685</v>
+      </c>
+      <c r="J13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>202</v>
+      </c>
+      <c r="C14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G14">
+        <v>2013168</v>
+      </c>
+      <c r="H14" s="1">
+        <v>44396.628147997682</v>
+      </c>
+      <c r="J14" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>201</v>
+      </c>
+      <c r="C15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G15">
+        <v>2013168</v>
+      </c>
+      <c r="H15" s="1">
+        <v>44396.628148611111</v>
+      </c>
+      <c r="J15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>202</v>
+      </c>
+      <c r="C16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G16">
+        <v>2013168</v>
+      </c>
+      <c r="H16" s="1">
+        <v>44396.628149456017</v>
+      </c>
+      <c r="J16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>555</v>
+      </c>
+      <c r="C17" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G17">
+        <v>2013168</v>
+      </c>
+      <c r="H17" s="1">
+        <v>44396.628149999997</v>
+      </c>
+      <c r="J17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>556</v>
+      </c>
+      <c r="C18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18">
+        <v>20</v>
+      </c>
+      <c r="F18" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G18">
+        <v>2013168</v>
+      </c>
+      <c r="H18" s="1">
+        <v>44396.628150578705</v>
+      </c>
+      <c r="J18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>555</v>
+      </c>
+      <c r="C19" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" t="s">
+        <v>149</v>
+      </c>
+      <c r="E19">
+        <v>19</v>
+      </c>
+      <c r="F19" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G19">
+        <v>2013168</v>
+      </c>
+      <c r="H19" s="1">
+        <v>44396.628151192126</v>
+      </c>
+      <c r="J19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>556</v>
+      </c>
+      <c r="C20" t="s">
+        <v>168</v>
+      </c>
+      <c r="D20" t="s">
+        <v>152</v>
+      </c>
+      <c r="E20">
+        <v>19</v>
+      </c>
+      <c r="F20" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G20">
+        <v>2013168</v>
+      </c>
+      <c r="H20" s="1">
+        <v>44396.628151851852</v>
+      </c>
+      <c r="J20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>551</v>
+      </c>
+      <c r="C21" t="s">
+        <v>169</v>
+      </c>
+      <c r="D21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21">
+        <v>6</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G21">
+        <v>2013168</v>
+      </c>
+      <c r="H21" s="1">
+        <v>44396.62815246528</v>
+      </c>
+      <c r="J21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>552</v>
+      </c>
+      <c r="C22" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22">
+        <v>6</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G22">
+        <v>2013168</v>
+      </c>
+      <c r="H22" s="1">
+        <v>44396.62815300926</v>
+      </c>
+      <c r="J22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>201</v>
+      </c>
+      <c r="C23" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" t="s">
+        <v>149</v>
+      </c>
+      <c r="E23">
+        <v>12</v>
+      </c>
+      <c r="F23" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G23">
+        <v>2013168</v>
+      </c>
+      <c r="H23" s="1">
+        <v>44396.62815355324</v>
+      </c>
+      <c r="J23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>202</v>
+      </c>
+      <c r="C24" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24">
+        <v>12</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G24">
+        <v>2013168</v>
+      </c>
+      <c r="H24" s="1">
+        <v>44396.628154166669</v>
+      </c>
+      <c r="J24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>701</v>
+      </c>
+      <c r="C25" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E25">
+        <v>18</v>
+      </c>
+      <c r="F25" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G25">
+        <v>2013168</v>
+      </c>
+      <c r="H25" s="1">
+        <v>44396.628154710648</v>
+      </c>
+      <c r="J25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>702</v>
+      </c>
+      <c r="C26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D26" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26">
+        <v>18</v>
+      </c>
+      <c r="F26" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G26">
+        <v>2013168</v>
+      </c>
+      <c r="H26" s="1">
+        <v>44396.628155243059</v>
+      </c>
+      <c r="J26" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>701</v>
+      </c>
+      <c r="C27" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27">
+        <v>17</v>
+      </c>
+      <c r="F27" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G27">
+        <v>2013168</v>
+      </c>
+      <c r="H27" s="1">
+        <v>44396.62815582176</v>
+      </c>
+      <c r="J27" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>702</v>
+      </c>
+      <c r="C28" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28">
+        <v>17</v>
+      </c>
+      <c r="F28" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G28">
+        <v>2013168</v>
+      </c>
+      <c r="H28" s="1">
+        <v>44396.628156481478</v>
+      </c>
+      <c r="J28" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>559</v>
+      </c>
+      <c r="C29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D29" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29">
+        <v>25</v>
+      </c>
+      <c r="F29" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G29">
+        <v>2013168</v>
+      </c>
+      <c r="H29" s="1">
+        <v>44396.628157094907</v>
+      </c>
+      <c r="J29" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>560</v>
+      </c>
+      <c r="C30" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30">
+        <v>25</v>
+      </c>
+      <c r="F30" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G30">
+        <v>2013168</v>
+      </c>
+      <c r="H30" s="1">
+        <v>44396.628157719904</v>
+      </c>
+      <c r="J30" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>201</v>
+      </c>
+      <c r="C31" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" t="s">
+        <v>149</v>
+      </c>
+      <c r="E31">
+        <v>7</v>
+      </c>
+      <c r="F31" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G31">
+        <v>2013168</v>
+      </c>
+      <c r="H31" s="1">
+        <v>44396.628158252315</v>
+      </c>
+      <c r="J31" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32">
+        <v>202</v>
+      </c>
+      <c r="C32" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" t="s">
+        <v>152</v>
+      </c>
+      <c r="E32">
+        <v>7</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G32">
+        <v>2013168</v>
+      </c>
+      <c r="H32" s="1">
+        <v>44396.628158796295</v>
+      </c>
+      <c r="J32" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>201</v>
+      </c>
+      <c r="C33" t="s">
+        <v>181</v>
+      </c>
+      <c r="D33" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33">
+        <v>9</v>
+      </c>
+      <c r="F33" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G33">
+        <v>2013168</v>
+      </c>
+      <c r="H33" s="1">
+        <v>44396.628159375003</v>
+      </c>
+      <c r="J33" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34">
+        <v>202</v>
+      </c>
+      <c r="C34" t="s">
+        <v>182</v>
+      </c>
+      <c r="D34" t="s">
+        <v>152</v>
+      </c>
+      <c r="E34">
+        <v>9</v>
+      </c>
+      <c r="F34" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G34">
+        <v>2013168</v>
+      </c>
+      <c r="H34" s="1">
+        <v>44396.628159988424</v>
+      </c>
+      <c r="J34" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35">
+        <v>201</v>
+      </c>
+      <c r="C35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35">
+        <v>10</v>
+      </c>
+      <c r="F35" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G35">
+        <v>2013168</v>
+      </c>
+      <c r="H35" s="1">
+        <v>44396.628160682871</v>
+      </c>
+      <c r="J35" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36">
+        <v>202</v>
+      </c>
+      <c r="C36" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36">
+        <v>10</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G36">
+        <v>2013168</v>
+      </c>
+      <c r="H36" s="1">
+        <v>44396.628161307868</v>
+      </c>
+      <c r="J36" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>201</v>
+      </c>
+      <c r="C37" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37">
+        <v>8</v>
+      </c>
+      <c r="F37" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G37">
+        <v>2013168</v>
+      </c>
+      <c r="H37" s="1">
+        <v>44396.628161886576</v>
+      </c>
+      <c r="J37" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38">
+        <v>202</v>
+      </c>
+      <c r="C38" t="s">
+        <v>186</v>
+      </c>
+      <c r="D38" t="s">
+        <v>152</v>
+      </c>
+      <c r="E38">
+        <v>8</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G38">
+        <v>2013168</v>
+      </c>
+      <c r="H38" s="1">
+        <v>44396.628162581015</v>
+      </c>
+      <c r="J38" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39">
+        <v>201</v>
+      </c>
+      <c r="C39" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" t="s">
+        <v>149</v>
+      </c>
+      <c r="E39">
+        <v>13</v>
+      </c>
+      <c r="F39" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G39">
+        <v>2013168</v>
+      </c>
+      <c r="H39" s="1">
+        <v>44396.628163229165</v>
+      </c>
+      <c r="J39" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40">
+        <v>202</v>
+      </c>
+      <c r="C40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D40" t="s">
+        <v>152</v>
+      </c>
+      <c r="E40">
+        <v>13</v>
+      </c>
+      <c r="F40" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G40">
+        <v>2013168</v>
+      </c>
+      <c r="H40" s="1">
+        <v>44396.62816385417</v>
+      </c>
+      <c r="J40" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41">
+        <v>201</v>
+      </c>
+      <c r="C41" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" t="s">
+        <v>149</v>
+      </c>
+      <c r="E41">
+        <v>11</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G41">
+        <v>2013168</v>
+      </c>
+      <c r="H41" s="1">
+        <v>44396.628164467591</v>
+      </c>
+      <c r="J41" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42">
+        <v>202</v>
+      </c>
+      <c r="C42" t="s">
+        <v>190</v>
+      </c>
+      <c r="D42" t="s">
+        <v>152</v>
+      </c>
+      <c r="E42">
+        <v>11</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G42">
+        <v>2013168</v>
+      </c>
+      <c r="H42" s="1">
+        <v>44396.62816508102</v>
+      </c>
+      <c r="J42" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43">
+        <v>201</v>
+      </c>
+      <c r="C43" t="s">
+        <v>191</v>
+      </c>
+      <c r="D43" t="s">
+        <v>149</v>
+      </c>
+      <c r="E43">
+        <v>14</v>
+      </c>
+      <c r="F43" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G43">
+        <v>2013168</v>
+      </c>
+      <c r="H43" s="1">
+        <v>44396.628165740738</v>
+      </c>
+      <c r="J43" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44">
+        <v>202</v>
+      </c>
+      <c r="C44" t="s">
+        <v>192</v>
+      </c>
+      <c r="D44" t="s">
+        <v>152</v>
+      </c>
+      <c r="E44">
+        <v>14</v>
+      </c>
+      <c r="F44" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G44">
+        <v>2013168</v>
+      </c>
+      <c r="H44" s="1">
+        <v>44396.628166354167</v>
+      </c>
+      <c r="J44" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45">
+        <v>201</v>
+      </c>
+      <c r="C45" t="s">
+        <v>193</v>
+      </c>
+      <c r="D45" t="s">
+        <v>149</v>
+      </c>
+      <c r="E45">
+        <v>15</v>
+      </c>
+      <c r="F45" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G45">
+        <v>2013168</v>
+      </c>
+      <c r="H45" s="1">
+        <v>44396.628166932867</v>
+      </c>
+      <c r="J45" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46">
+        <v>202</v>
+      </c>
+      <c r="C46" t="s">
+        <v>194</v>
+      </c>
+      <c r="D46" t="s">
+        <v>152</v>
+      </c>
+      <c r="E46">
+        <v>15</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G46">
+        <v>2013168</v>
+      </c>
+      <c r="H46" s="1">
+        <v>44396.628167476854</v>
+      </c>
+      <c r="J46" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>47</v>
+      </c>
+      <c r="B47">
+        <v>201</v>
+      </c>
+      <c r="C47" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" t="s">
+        <v>149</v>
+      </c>
+      <c r="E47">
+        <v>21</v>
+      </c>
+      <c r="F47" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G47">
+        <v>2013168</v>
+      </c>
+      <c r="H47" s="1">
+        <v>44396.628168020834</v>
+      </c>
+      <c r="J47" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>48</v>
+      </c>
+      <c r="B48">
+        <v>202</v>
+      </c>
+      <c r="C48" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48" t="s">
+        <v>152</v>
+      </c>
+      <c r="E48">
+        <v>21</v>
+      </c>
+      <c r="F48" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G48">
+        <v>2013168</v>
+      </c>
+      <c r="H48" s="1">
+        <v>44396.628168599535</v>
+      </c>
+      <c r="J48" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>49</v>
+      </c>
+      <c r="B49">
+        <v>201</v>
+      </c>
+      <c r="C49" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" t="s">
+        <v>149</v>
+      </c>
+      <c r="E49">
+        <v>23</v>
+      </c>
+      <c r="F49" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G49">
+        <v>2013168</v>
+      </c>
+      <c r="H49" s="1">
+        <v>44396.628169293981</v>
+      </c>
+      <c r="J49" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50">
+        <v>202</v>
+      </c>
+      <c r="C50" t="s">
+        <v>198</v>
+      </c>
+      <c r="D50" t="s">
+        <v>152</v>
+      </c>
+      <c r="E50">
+        <v>23</v>
+      </c>
+      <c r="F50" s="1">
+        <v>44396.626388888886</v>
+      </c>
+      <c r="G50">
+        <v>2013168</v>
+      </c>
+      <c r="H50" s="1">
+        <v>44396.628169872682</v>
+      </c>
+      <c r="J50" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>51</v>
+      </c>
+      <c r="B51">
+        <v>311</v>
+      </c>
+      <c r="C51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D51" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G51">
+        <v>2013168</v>
+      </c>
+      <c r="H51" s="1">
+        <v>44502</v>
+      </c>
+      <c r="I51" t="s">
+        <v>44</v>
+      </c>
+      <c r="J51" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>52</v>
+      </c>
+      <c r="B52">
+        <v>344</v>
+      </c>
+      <c r="C52" t="s">
+        <v>200</v>
+      </c>
+      <c r="D52" t="s">
+        <v>149</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52" s="1">
+        <v>44502</v>
+      </c>
+      <c r="G52">
+        <v>2013168</v>
+      </c>
+      <c r="H52" s="1">
+        <v>44502</v>
+      </c>
+      <c r="I52" t="s">
+        <v>44</v>
+      </c>
+      <c r="J52" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>